--- a/artfynd/A 3005-2022 artfynd.xlsx
+++ b/artfynd/A 3005-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3005-2022 artfynd.xlsx
+++ b/artfynd/A 3005-2022 artfynd.xlsx
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100579223</v>
+        <v>112702664</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-Olssvarttjärnen, Ol-Olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447094.0626025737</v>
+        <v>446906</v>
       </c>
       <c r="R2" t="n">
-        <v>7034246.723405617</v>
+        <v>7033973</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100581144</v>
+        <v>100579164</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447001.6609603004</v>
+        <v>447094</v>
       </c>
       <c r="R3" t="n">
-        <v>7033973.775402402</v>
+        <v>7034247</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100579164</v>
+        <v>100581144</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447094.0626025737</v>
+        <v>447001</v>
       </c>
       <c r="R4" t="n">
-        <v>7034246.723405617</v>
+        <v>7033974</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,54 +969,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100579149</v>
+        <v>112701289</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-Olssvarttjärnen, Ol-Olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447094.0626025737</v>
+        <v>446997</v>
       </c>
       <c r="R5" t="n">
-        <v>7034246.723405617</v>
+        <v>7034045</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102575840</v>
+        <v>100579223</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,34 +1078,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447056.3301800016</v>
+        <v>447094</v>
       </c>
       <c r="R6" t="n">
-        <v>7034242.423019211</v>
+        <v>7034247</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102575821</v>
+        <v>102575832</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447110.2873958331</v>
+        <v>446965</v>
       </c>
       <c r="R7" t="n">
-        <v>7034306.0042443</v>
+        <v>7034185</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,19 +1233,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102575847</v>
+        <v>112213236</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,37 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446959.885649454</v>
+        <v>447095</v>
       </c>
       <c r="R8" t="n">
-        <v>7034023.276227505</v>
+        <v>7034251</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,22 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,65 +1347,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102575841</v>
+        <v>112213261</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447056.3301800016</v>
+        <v>446987</v>
       </c>
       <c r="R9" t="n">
-        <v>7034242.423019211</v>
+        <v>7034048</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,22 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,62 +1444,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102575823</v>
+        <v>115890723</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>4412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Tjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446899.8235007018</v>
+        <v>447129</v>
       </c>
       <c r="R10" t="n">
-        <v>7033970.539871066</v>
+        <v>7034271</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,22 +1524,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,71 +1538,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102575822</v>
+        <v>112213237</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446899.8235007018</v>
+        <v>446938</v>
       </c>
       <c r="R11" t="n">
-        <v>7033970.539871066</v>
+        <v>7033939</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,22 +1622,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,65 +1642,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102575820</v>
+        <v>112213241</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447110.2873958331</v>
+        <v>446990</v>
       </c>
       <c r="R12" t="n">
-        <v>7034306.0042443</v>
+        <v>7034063</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,22 +1719,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,49 +1739,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112213237</v>
+        <v>112213247</v>
       </c>
       <c r="B13" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446938</v>
+        <v>447156</v>
       </c>
       <c r="R13" t="n">
-        <v>7033939</v>
+        <v>7034283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,53 +1848,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112213236</v>
+        <v>102575820</v>
       </c>
       <c r="B14" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447095</v>
+        <v>447110</v>
       </c>
       <c r="R14" t="n">
-        <v>7034251</v>
+        <v>7034306</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,12 +1913,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,27 +1933,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112213248</v>
+        <v>102575822</v>
       </c>
       <c r="B15" t="n">
-        <v>89133</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,37 +1956,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256335</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447082</v>
+        <v>446900</v>
       </c>
       <c r="R15" t="n">
-        <v>7034277</v>
+        <v>7033970</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,12 +2010,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,72 +2024,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112213261</v>
+        <v>102575840</v>
       </c>
       <c r="B16" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446988</v>
+        <v>447056</v>
       </c>
       <c r="R16" t="n">
-        <v>7034047</v>
+        <v>7034243</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,12 +2107,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,62 +2127,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112213241</v>
+        <v>112213252</v>
       </c>
       <c r="B17" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446991</v>
+        <v>446988</v>
       </c>
       <c r="R17" t="n">
-        <v>7034063</v>
+        <v>7034002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2422,50 +2241,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112213247</v>
+        <v>112213265</v>
       </c>
       <c r="B18" t="n">
-        <v>89143</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447157</v>
+        <v>446905</v>
       </c>
       <c r="R18" t="n">
-        <v>7034283</v>
+        <v>7033928</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,58 +2343,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112213252</v>
+        <v>102575821</v>
       </c>
       <c r="B19" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446988</v>
+        <v>447110</v>
       </c>
       <c r="R19" t="n">
-        <v>7034003</v>
+        <v>7034306</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2599,12 +2408,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,70 +2428,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112213265</v>
+        <v>102575823</v>
       </c>
       <c r="B20" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-olssvarttjärnen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446905</v>
+        <v>446900</v>
       </c>
       <c r="R20" t="n">
-        <v>7033927</v>
+        <v>7033970</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,12 +2505,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,66 +2525,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112702664</v>
+        <v>102575841</v>
       </c>
       <c r="B21" t="n">
-        <v>74052</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ol-Olssvarttjärnen (Ol-Olssvarttjärnen), Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446906</v>
+        <v>447056</v>
       </c>
       <c r="R21" t="n">
-        <v>7033974</v>
+        <v>7034243</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2809,12 +2602,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,66 +2622,61 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112701289</v>
+        <v>100579149</v>
       </c>
       <c r="B22" t="n">
-        <v>89796</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ol-Olssvarttjärnen (Ol-Olssvarttjärnen), Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446997</v>
+        <v>447094</v>
       </c>
       <c r="R22" t="n">
-        <v>7034046</v>
+        <v>7034247</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,12 +2700,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,27 +2720,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112701293</v>
+        <v>112213248</v>
       </c>
       <c r="B23" t="n">
-        <v>90136</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,35 +2743,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>256335</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ol-Olssvarttjärnen (Ol-Olssvarttjärnen), Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446997</v>
+        <v>447082</v>
       </c>
       <c r="R23" t="n">
-        <v>7034046</v>
+        <v>7034277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,12 +2797,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,55 +2811,46 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115890723</v>
+        <v>112701293</v>
       </c>
       <c r="B24" t="n">
-        <v>87189</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
+        <v>6331024</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Skeletocutis delicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,17 +2859,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tjärnhön, Jmt</t>
+          <t>Ol-Olssvarttjärnen, Ol-Olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447129</v>
+        <v>446997</v>
       </c>
       <c r="R24" t="n">
-        <v>7034271</v>
+        <v>7034045</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3132,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">

--- a/artfynd/A 3005-2022 artfynd.xlsx
+++ b/artfynd/A 3005-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112702664</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100579164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100581144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112701289</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100579223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575832</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213261</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115890723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213237</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213241</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213247</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575820</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575822</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575840</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213252</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2340,6 +2425,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213265</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,6 +2527,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575823</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2631,6 +2731,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575841</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100579149</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2827,6 +2937,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213248</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,8 +3038,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112701293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>